--- a/satisfaction_surveys/037_marriage_satisfaction_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/037_marriage_satisfaction_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all satisfied'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat agree'}</t>
+          <t>Somewhat agree</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat disagree'}</t>
+          <t>Somewhat disagree</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>conflicts_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>almost_never</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly disagree'}</t>
+          <t>Almost never</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'almost_never'}</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Almost never'}</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_once_a_week'}</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Less than once a week'}</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_times_a_week'}</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '1-2 times a week'}</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'3-4_times_a_week'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '3-4 times a week'}</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>conflicts_choices</t>
+          <t>conflict_resolution_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Almost always'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Not satisfied'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>relationship_health_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_satisfied'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all satisfied'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>relationship_health_choices</t>
+          <t>partner_involvement_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'very_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Very important'}</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_important'}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Not very important'}</t>
+          <t>Not at all important</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>partner_involvement_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_important'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all important'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Not satisfied'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>decision_making_choices</t>
+          <t>partner_support_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Not satisfied'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>partner_support_choices</t>
+          <t>relationship_stability_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_satisfied'}</t>
+          <t>very_stable</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all satisfied'}</t>
+          <t>Very stable</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'very_stable'}</t>
+          <t>somewhat_stable</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Very stable'}</t>
+          <t>Somewhat stable</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_stable'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat stable'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_unstable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat unstable</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unstable'}</t>
+          <t>very_unstable</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat unstable'}</t>
+          <t>Very unstable</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>relationship_stability_choices</t>
+          <t>conflict_resolution_strategy_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'very_unstable'}</t>
+          <t>active_listening</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Very unstable'}</t>
+          <t>Active listening</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'active_listening'}</t>
+          <t>compromise</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Active listening'}</t>
+          <t>Compromise</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'compromise'}</t>
+          <t>avoidance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Compromise'}</t>
+          <t>Avoidance</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'avoidance'}</t>
+          <t>anger</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Avoidance'}</t>
+          <t>Anger</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1845,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'anger'}</t>
+          <t>give_up</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Anger'}</t>
+          <t>Give up</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>conflict_resolution_strategy_choices</t>
+          <t>partner_participation_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'give_up'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Give up'}</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Almost always'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>partner_participation_choices</t>
+          <t>shared_responsibilities_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'financial'}</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Financial'}</t>
+          <t>Emotional</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'emotional'}</t>
+          <t>household</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional'}</t>
+          <t>Household</t>
         </is>
       </c>
     </row>
@@ -1998,29 +1998,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'household'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Household'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>shared_responsibilities_choices</t>
+          <t>partner_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -2066,29 +2066,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Not satisfied'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>partner_satisfaction_2_choices</t>
+          <t>partner_satisfaction_3_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -2134,29 +2134,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Not satisfied'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>partner_satisfaction_3_choices</t>
+          <t>communication_quality_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_satisfied'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all satisfied'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -2202,29 +2202,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>communication_quality_choices</t>
+          <t>partner_happiness_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>very_happy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Very happy</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'very_happy'}</t>
+          <t>somewhat_happy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Very happy'}</t>
+          <t>Somewhat happy</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_happy'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat happy'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_unhappy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat unhappy</t>
         </is>
       </c>
     </row>
@@ -2287,29 +2287,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unhappy'}</t>
+          <t>very_unhappy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat unhappy'}</t>
+          <t>Very unhappy</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>partner_happiness_choices</t>
+          <t>relationship_growth_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'very_unhappy'}</t>
+          <t>very_grown</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'Very unhappy'}</t>
+          <t>Very grown</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'very_grown'}</t>
+          <t>somewhat_grown</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'Very grown'}</t>
+          <t>Somewhat grown</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_grown'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat grown'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_ungrown</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat ungrown</t>
         </is>
       </c>
     </row>
@@ -2372,29 +2372,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_ungrown'}</t>
+          <t>very_ungrown</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat ungrown'}</t>
+          <t>Very ungrown</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>relationship_growth_choices</t>
+          <t>conflict_frequency_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'label':_'very_ungrown'}</t>
+          <t>almost_never</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'label': 'Very ungrown'}</t>
+          <t>Almost never</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'label':_'almost_never'}</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'label': 'Almost never'}</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_once_a_week'}</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'label': 'Less than once a week'}</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_times_a_week'}</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'label': '1-2 times a week'}</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
@@ -2457,29 +2457,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'label':_'3-4_times_a_week'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'label': '3-4 times a week'}</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>conflict_frequency_choices</t>
+          <t>partner_involvement_frequency_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'label': 'Almost always'}</t>
+          <t>Very often</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'label':_'very_often'}</t>
+          <t>somewhat_often</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'label': 'Very often'}</t>
+          <t>Somewhat often</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_often'}</t>
+          <t>not_very_often</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat often'}</t>
+          <t>Not very often</t>
         </is>
       </c>
     </row>
@@ -2525,29 +2525,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_often'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'label': 'Not very often'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>partner_involvement_frequency_choices</t>
+          <t>partner_satisfaction_4_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -2593,29 +2593,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'label': 'Not satisfied'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>partner_satisfaction_4_choices</t>
+          <t>partner_satisfaction_5_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
@@ -2661,29 +2661,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'label': 'Not satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>partner_satisfaction_5_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>{'label':_'not_at_all_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>{'label': 'Not at all satisfied'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
